--- a/docs/data_dictionary.xlsx
+++ b/docs/data_dictionary.xlsx
@@ -652,7 +652,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>female_population_15_44</t>
+          <t>female_population_15_19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sum of the CDC fertility-rate denominator population, 2017-2021.</t>
+          <t>Sum of the CDC fertility-rate denominator, 2017-2021. WONDER subsets the 15-44 denominator by the same mother's-age filter as the numerator (query caveat 4), so with Age of Mother = 15-19 this is females aged 15-19 (e.g. Alabama White 2019 = 99,059), not 15-44.</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>births_teen / female_population_15_44 x 1,000, computed from the 5-year sums (not an average of annual rates).</t>
+          <t>births_teen / female_population_15_19 x 1,000 = births per 1,000 females aged 15-19 (age-specific rate), computed from the 5-year sums (not an average of annual rates).</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>insurance_rate</t>
+          <t>uninsured_rate</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -805,7 +805,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>insurance_rate_moe</t>
+          <t>uninsured_rate_moe</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ACS margin of error for insurance_rate</t>
+          <t>ACS margin of error for uninsured_rate</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Source tables for poverty_rate/insurance_rate, including the age-band mismatch between S1701 (under 18) and S2701 (under 19)</t>
+          <t>Source tables for poverty_rate/uninsured_rate, including the age-band mismatch between S1701 (under 18) and S2701 (under 19)</t>
         </is>
       </c>
     </row>
